--- a/SGC-CKN/Excel/0021cd0f-4f81-4df1-bc89-5a884957604d_Cọc_số_N1-109_P7-109_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/0021cd0f-4f81-4df1-bc89-5a884957604d_Cọc_số_N1-109_P7-109_D800_20-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
   <si>
     <t>Dự án</t>
   </si>
@@ -137,9 +137,6 @@
 20/03/2026</t>
   </si>
   <si>
-    <t>Chiều dài tính từ độ sâu cộng dồn</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -178,7 +175,7 @@
 20/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">07:10
+    <t xml:space="preserve">07:30
 20/03/2026</t>
   </si>
   <si>
@@ -188,11 +185,11 @@
     <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
-    <t xml:space="preserve">07:11
+    <t xml:space="preserve">07:31
 20/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">08:57
+    <t xml:space="preserve">08:59
 20/03/2026</t>
   </si>
   <si>
@@ -1327,24 +1324,24 @@
         <v>8.34</v>
       </c>
       <c r="K13" s="13" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
       <c r="C14" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D14" s="17" t="s">
         <v>41</v>
       </c>
-      <c r="D14" s="17" t="s">
+      <c r="E14" s="17" t="s">
         <v>42</v>
-      </c>
-      <c r="E14" s="17" t="s">
-        <v>43</v>
       </c>
       <c r="F14" s="15">
         <v>-16.7</v>
@@ -1362,24 +1359,24 @@
         <v>8.9</v>
       </c>
       <c r="K14" s="16" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" s="18" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
       <c r="C15" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="D15" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="E15" s="20" t="s">
         <v>46</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>47</v>
       </c>
       <c r="F15" s="18">
         <v>-21</v>
@@ -1397,24 +1394,24 @@
         <v>14</v>
       </c>
       <c r="K15" s="19" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="21" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B16" s="21" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="D16" s="23" t="s">
+      <c r="E16" s="23" t="s">
         <v>50</v>
-      </c>
-      <c r="E16" s="23" t="s">
-        <v>51</v>
       </c>
       <c r="F16" s="21">
         <v>-28</v>
@@ -1423,33 +1420,33 @@
         <v>-35</v>
       </c>
       <c r="H16" s="21">
-        <v>0.63</v>
+        <v>0.97</v>
       </c>
       <c r="I16" s="21">
         <v>7</v>
       </c>
       <c r="J16" s="8">
-        <v>11.05</v>
+        <v>7.24</v>
       </c>
       <c r="K16" s="22" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="D17" s="26" t="s">
         <v>53</v>
       </c>
-      <c r="D17" s="26" t="s">
+      <c r="E17" s="26" t="s">
         <v>54</v>
-      </c>
-      <c r="E17" s="26" t="s">
-        <v>55</v>
       </c>
       <c r="F17" s="24">
         <v>-35</v>
@@ -1458,13 +1455,13 @@
         <v>-37.5</v>
       </c>
       <c r="H17" s="24">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="I17" s="24">
         <v>2.5</v>
       </c>
       <c r="J17" s="27">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
       <c r="K17" s="25" t="s">
         <v>30</v>
@@ -1472,19 +1469,19 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="E18" s="30" t="s">
         <v>58</v>
-      </c>
-      <c r="E18" s="30" t="s">
-        <v>59</v>
       </c>
       <c r="F18" s="28">
         <v>-37.5</v>
@@ -1507,19 +1504,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>62</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>63</v>
       </c>
       <c r="F19" s="31">
         <v>-39</v>
@@ -1542,19 +1539,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>66</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>67</v>
       </c>
       <c r="F20" s="34">
         <v>-43.2</v>
@@ -1577,7 +1574,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="37" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B23" s="37"/>
       <c r="C23" s="37"/>
@@ -1683,31 +1680,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>75</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1805,7 +1802,7 @@
         <v>11</v>
       </c>
       <c r="C5" s="16" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D5" s="15">
         <v>1</v>
@@ -1834,7 +1831,7 @@
         <v>11</v>
       </c>
       <c r="C6" s="19" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D6" s="18">
         <v>1</v>
@@ -1863,7 +1860,7 @@
         <v>11</v>
       </c>
       <c r="C7" s="22" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D7" s="21">
         <v>1</v>
@@ -1875,13 +1872,13 @@
         <v>-35</v>
       </c>
       <c r="G7" s="21">
-        <v>0.63</v>
+        <v>0.97</v>
       </c>
       <c r="H7" s="21">
         <v>7</v>
       </c>
       <c r="I7" s="8">
-        <v>11.05</v>
+        <v>7.24</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1892,7 +1889,7 @@
         <v>11</v>
       </c>
       <c r="C8" s="25" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D8" s="24">
         <v>1</v>
@@ -1904,13 +1901,13 @@
         <v>-37.5</v>
       </c>
       <c r="G8" s="24">
-        <v>1.77</v>
+        <v>1.47</v>
       </c>
       <c r="H8" s="24">
         <v>2.5</v>
       </c>
       <c r="I8" s="27">
-        <v>1.42</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1921,7 +1918,7 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
@@ -1950,7 +1947,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1979,7 +1976,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -2002,7 +1999,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B12" s="39" t="s">
         <v>30</v>
@@ -2020,13 +2017,13 @@
         <v>-44.4</v>
       </c>
       <c r="G12" s="39">
-        <v>6.88</v>
+        <v>6.92</v>
       </c>
       <c r="H12" s="39">
         <v>43.9</v>
       </c>
       <c r="I12" s="39">
-        <v>6.38</v>
+        <v>6.35</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/0021cd0f-4f81-4df1-bc89-5a884957604d_Cọc_số_N1-109_P7-109_D800_20-03-2026.xlsx
+++ b/SGC-CKN/Excel/0021cd0f-4f81-4df1-bc89-5a884957604d_Cọc_số_N1-109_P7-109_D800_20-03-2026.xlsx
@@ -1557,16 +1557,16 @@
         <v>-43.2</v>
       </c>
       <c r="G20" s="34">
-        <v>-44.4</v>
+        <v>-44.7</v>
       </c>
       <c r="H20" s="34">
         <v>0.4</v>
       </c>
       <c r="I20" s="34">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="J20" s="27">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1985,16 +1985,16 @@
         <v>-43.2</v>
       </c>
       <c r="F11" s="34">
-        <v>-44.4</v>
+        <v>-44.7</v>
       </c>
       <c r="G11" s="34">
         <v>0.4</v>
       </c>
       <c r="H11" s="34">
-        <v>1.2</v>
+        <v>1.5</v>
       </c>
       <c r="I11" s="27">
-        <v>3</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -2014,16 +2014,16 @@
         <v>-0.5</v>
       </c>
       <c r="F12" s="39">
-        <v>-44.4</v>
+        <v>-44.7</v>
       </c>
       <c r="G12" s="39">
         <v>6.92</v>
       </c>
       <c r="H12" s="39">
-        <v>43.9</v>
+        <v>44.2</v>
       </c>
       <c r="I12" s="39">
-        <v>6.35</v>
+        <v>6.39</v>
       </c>
     </row>
   </sheetData>
